--- a/artifacts/BTC_USDT/metrics/BTC_USDT_metrics.xlsx
+++ b/artifacts/BTC_USDT/metrics/BTC_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15151743.29429434</v>
+        <v>10800419.08259912</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3892.524026167898</v>
+        <v>3286.399105799404</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3218.758064208505</v>
+        <v>2704.268618617362</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9164720170142953</v>
+        <v>0.9101122035016745</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.547714767393775</v>
+        <v>2.913524165886671</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88858.38635294119</v>
+        <v>93664.38844961239</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85898.96811575112</v>
+        <v>91330.5024302056</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89226.83508116571</v>
+        <v>92515.76700751708</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86133.55408391131</v>
+        <v>90117.48658527908</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/BTC_USDT/metrics/BTC_USDT_metrics.xlsx
+++ b/artifacts/BTC_USDT/metrics/BTC_USDT_metrics.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10800419.08259912</v>
+        <v>12084726.20503774</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3286.399105799404</v>
+        <v>3476.309279255478</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2704.268618617362</v>
+        <v>2876.049054661048</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9101122035016745</v>
+        <v>0.8975520720396997</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.913524165886671</v>
+        <v>3.049941781467156</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>93664.38844961239</v>
+        <v>93810.9257364341</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>91330.5024302056</v>
+        <v>91342.59476166873</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92515.76700751708</v>
+        <v>92673.8252774154</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90117.48658527908</v>
+        <v>90234.21010610716</v>
       </c>
     </row>
   </sheetData>
